--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\asociacionalmasbellas-web\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\asociacionalmasbellas.github.io\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -420,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
@@ -441,7 +441,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -455,18 +455,421 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -36,18 +36,34 @@
     <t>Fecha</t>
   </si>
   <si>
-    <t>Descripcion premio</t>
+    <t>Descripcion Rifa</t>
   </si>
   <si>
-    <t>Esta rifa financiará la rehabilitación de Vida para que pueda volver a andar.
-El premio son unos juguetes variados para perros junto con llaveros</t>
+    <t>Descripcion Premio</t>
+  </si>
+  <si>
+    <t>En esta nueva rifa hemos querido sobre todo enfocarnos en los juegos y entretenimientos de los peludos, siendo los siguientes objetos los rifados:
+- Tres llaveros cuquísimos en versión animales (esto para el dueño)
+- Mordedor de cuerda con pelota y ventosa
+- Peluche de León multicolor
+- Pelota de goma con texturas
+- Alfombra olfativa pequeña
+- Dos pelotas Kong con sonido
+- Alfombrilla de lamer
+Gracias por el donativo a Articupets</t>
+  </si>
+  <si>
+    <t>Con VIDA llevamos algo más de un año apostando por su vida, por su oportunidad de normalizar, por su oportunidad de caminar más que menos .....
+Por ello apostamos por una guardería próxima, La Huella Azul, donde está la única veterinaria fisioterapeuta que aceptó venir a domicilio y que durante aproximadamente 9 meses está realizando la rehabilitación del pequeño.
+Volvemos con una Rifa para intentar sostener la rehabilitación, Bonos de 10 sesiones a 875€ que duran sobre un mes.
+Gracias a vuestra participación y a vuestros generosos donativos hemos podido renovar los Bonos durante este tiempo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -60,6 +76,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,11 +131,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ConditionalFormatStyle" xfId="1"/>
@@ -420,15 +443,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="42.42578125" customWidth="1"/>
+    <col min="3" max="3" width="103.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,7 +462,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -453,7 +476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -461,7 +484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="165" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -469,65 +492,72 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="180" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>18</v>
       </c>
@@ -874,6 +904,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -9,17 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Colaboradores" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -58,12 +59,24 @@
 Volvemos con una Rifa para intentar sostener la rehabilitación, Bonos de 10 sesiones a 875€ que duran sobre un mes.
 Gracias a vuestra participación y a vuestros generosos donativos hemos podido renovar los Bonos durante este tiempo</t>
   </si>
+  <si>
+    <t>Colaborador</t>
+  </si>
+  <si>
+    <t>Enlace</t>
+  </si>
+  <si>
+    <t>ArticuPets</t>
+  </si>
+  <si>
+    <t>https://articupets.art/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -74,6 +87,7 @@
       <sz val="11"/>
       <color rgb="FF2B579A"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -83,6 +97,13 @@
     <font>
       <u/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -124,23 +145,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="ConditionalFormatStyle" xfId="1"/>
     <cellStyle name="HeaderStyle" xfId="2"/>
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -907,4 +931,37 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\asociacionalmasbellas.github.io\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\asociacionalmasbellas.github.io\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,12 +15,12 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Colaboradores" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>Descripcion Rifa</t>
+  </si>
+  <si>
+    <t>Con VIDA llevamos algo más de un año apostando por su vida, por su oportunidad de normalizar, por su oportunidad de caminar más que menos .....
+Por ello apostamos por una guardería próxima, La Huella Azul, donde está la única veterinaria fisioterapeuta que aceptó venir a domicilio y que durante aproximadamente 9 meses está realizando la rehabilitación del pequeño.
+Volvemos con una Rifa para intentar sostener la rehabilitación, Bonos de 10 sesiones a 875€ que duran sobre un mes.
+Gracias a vuestra participación y a vuestros generosos donativos hemos podido renovar los Bonos durante este tiempo</t>
   </si>
   <si>
     <t>Descripcion Premio</t>
@@ -54,12 +60,6 @@
 Gracias por el donativo a Articupets</t>
   </si>
   <si>
-    <t>Con VIDA llevamos algo más de un año apostando por su vida, por su oportunidad de normalizar, por su oportunidad de caminar más que menos .....
-Por ello apostamos por una guardería próxima, La Huella Azul, donde está la única veterinaria fisioterapeuta que aceptó venir a domicilio y que durante aproximadamente 9 meses está realizando la rehabilitación del pequeño.
-Volvemos con una Rifa para intentar sostener la rehabilitación, Bonos de 10 sesiones a 875€ que duran sobre un mes.
-Gracias a vuestra participación y a vuestros generosos donativos hemos podido renovar los Bonos durante este tiempo</t>
-  </si>
-  <si>
     <t>Colaborador</t>
   </si>
   <si>
@@ -70,25 +70,19 @@
   </si>
   <si>
     <t>https://articupets.art/</t>
+  </si>
+  <si>
+    <t>Clínica Veterinària Petits i Peluts</t>
+  </si>
+  <si>
+    <t>https://www.clinicaveterinariapetitsipeluts.com/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF2B579A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -98,25 +92,26 @@
       <u/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF2B579A"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -126,57 +121,40 @@
     </fill>
   </fills>
   <borders count="2">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color rgb="FF2B579A"/>
       </right>
-      <top/>
       <bottom style="medium">
         <color rgb="FF2B579A"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="ConditionalFormatStyle" xfId="1"/>
-    <cellStyle name="HeaderStyle" xfId="2"/>
-    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="ConditionalFormatStyle" xfId="2"/>
+    <cellStyle name="HeaderStyle" xfId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -185,10 +163,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -320,6 +298,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -343,10 +322,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -355,13 +335,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -437,6 +417,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -456,26 +437,24 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F84"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.132813" defaultRowHeight="14.8"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="103.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.40625" customWidth="1"/>
+    <col min="2" max="2" width="23.86328" customWidth="1"/>
+    <col min="3" max="3" width="103.1328" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +465,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" ht="15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -500,7 +479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" ht="15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -508,7 +487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+    <row r="4" ht="165">
       <c r="A4">
         <v>3</v>
       </c>
@@ -516,433 +495,431 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="180">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" ht="15">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" ht="15">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" ht="15">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" ht="15">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" ht="15">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" ht="15">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" ht="15">
       <c r="A12">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" ht="15">
       <c r="A13">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" ht="15">
       <c r="A14">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" ht="15">
       <c r="A15">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" ht="15">
       <c r="A16">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15">
       <c r="A17">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15">
       <c r="A18">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15">
       <c r="A19">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15">
       <c r="A20">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15">
       <c r="A21">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15">
       <c r="A22">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15">
       <c r="A23">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15">
       <c r="A24">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15">
       <c r="A25">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15">
       <c r="A26">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15">
       <c r="A27">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15">
       <c r="A28">
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15">
       <c r="A29">
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15">
       <c r="A30">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15">
       <c r="A31">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15">
       <c r="A32">
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15">
       <c r="A33">
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15">
       <c r="A34">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15">
       <c r="A35">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15">
       <c r="A36">
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15">
       <c r="A37">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15">
       <c r="A38">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15">
       <c r="A39">
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15">
       <c r="A40">
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15">
       <c r="A41">
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15">
       <c r="A42">
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15">
       <c r="A43">
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15">
       <c r="A44">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15">
       <c r="A45">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15">
       <c r="A46">
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15">
       <c r="A47">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15">
       <c r="A48">
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15">
       <c r="A49">
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15">
       <c r="A50">
         <v>119</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15">
       <c r="A51">
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15">
       <c r="A52">
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15">
       <c r="A53">
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15">
       <c r="A54">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15">
       <c r="A55">
         <v>134</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15">
       <c r="A56">
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15">
       <c r="A57">
         <v>139</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" ht="15">
       <c r="A58">
         <v>143</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15">
       <c r="A59">
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15">
       <c r="A60">
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15">
       <c r="A61">
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15">
       <c r="A62">
         <v>156</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15">
       <c r="A63">
         <v>163</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15">
       <c r="A64">
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" ht="15">
       <c r="A65">
         <v>167</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15">
       <c r="A66">
         <v>170</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15">
       <c r="A67">
         <v>176</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15">
       <c r="A68">
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15">
       <c r="A69">
         <v>183</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15">
       <c r="A70">
         <v>195</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15">
       <c r="A71">
         <v>198</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15">
       <c r="A72">
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15">
       <c r="A73">
         <v>208</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15">
       <c r="A74">
         <v>213</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15">
       <c r="A75">
         <v>208</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15">
       <c r="A76">
         <v>212</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15">
       <c r="A77">
         <v>213</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15">
       <c r="A78">
         <v>215</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15">
       <c r="A79">
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15">
       <c r="A80">
         <v>233</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15">
       <c r="A81">
         <v>239</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15">
       <c r="A82">
         <v>240</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" ht="15">
       <c r="A83">
         <v>246</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" ht="15">
       <c r="A84">
         <v>250</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" paperSize="9" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.8"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.54297" customWidth="1"/>
+    <col min="2" max="2" width="27.54297" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -950,18 +927,25 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\asociacionalmasbellas.github.io\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\PaginaWeb\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Colaboradores" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -81,8 +81,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -105,6 +105,11 @@
       <color rgb="FF2B579A"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -121,20 +126,29 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF2B579A"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF2B579A"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -148,13 +162,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="ConditionalFormatStyle" xfId="2"/>
     <cellStyle name="HeaderStyle" xfId="3"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -163,10 +185,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -298,7 +320,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -322,11 +343,10 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -335,13 +355,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -417,7 +437,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -437,24 +456,26 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.132813" defaultRowHeight="14.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F84"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.40625" customWidth="1"/>
-    <col min="2" max="2" width="23.86328" customWidth="1"/>
-    <col min="3" max="3" width="103.1328" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="103.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -465,7 +486,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" ht="15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -479,7 +500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -487,7 +508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="165">
+    <row r="4" spans="1:6" ht="165" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -498,7 +519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="180">
+    <row r="5" spans="1:6" ht="180" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -510,416 +531,418 @@
       </c>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" ht="15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="15">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="15">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="15">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" ht="15">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="15">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
     </row>
-    <row r="13" ht="15">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
     </row>
-    <row r="14" ht="15">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>16</v>
       </c>
     </row>
-    <row r="15" ht="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>17</v>
       </c>
     </row>
-    <row r="16" ht="15">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>18</v>
       </c>
     </row>
-    <row r="17" ht="15">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26</v>
       </c>
     </row>
-    <row r="20" ht="15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>27</v>
       </c>
     </row>
-    <row r="21" ht="15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>28</v>
       </c>
     </row>
-    <row r="22" ht="15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>29</v>
       </c>
     </row>
-    <row r="23" ht="15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>38</v>
       </c>
     </row>
-    <row r="24" ht="15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>43</v>
       </c>
     </row>
-    <row r="25" ht="15">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>45</v>
       </c>
     </row>
-    <row r="26" ht="15">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>53</v>
       </c>
     </row>
-    <row r="27" ht="15">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>58</v>
       </c>
     </row>
-    <row r="28" ht="15">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>59</v>
       </c>
     </row>
-    <row r="29" ht="15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>60</v>
       </c>
     </row>
-    <row r="30" ht="15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>63</v>
       </c>
     </row>
-    <row r="31" ht="15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>66</v>
       </c>
     </row>
-    <row r="32" ht="15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>67</v>
       </c>
     </row>
-    <row r="33" ht="15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>71</v>
       </c>
     </row>
-    <row r="34" ht="15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>74</v>
       </c>
     </row>
-    <row r="35" ht="15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>76</v>
       </c>
     </row>
-    <row r="36" ht="15">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>78</v>
       </c>
     </row>
-    <row r="37" ht="15">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>82</v>
       </c>
     </row>
-    <row r="38" ht="15">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>88</v>
       </c>
     </row>
-    <row r="39" ht="15">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>89</v>
       </c>
     </row>
-    <row r="40" ht="15">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>91</v>
       </c>
     </row>
-    <row r="41" ht="15">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>92</v>
       </c>
     </row>
-    <row r="42" ht="15">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>95</v>
       </c>
     </row>
-    <row r="43" ht="15">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>96</v>
       </c>
     </row>
-    <row r="44" ht="15">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>98</v>
       </c>
     </row>
-    <row r="45" ht="15">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>100</v>
       </c>
     </row>
-    <row r="46" ht="15">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>103</v>
       </c>
     </row>
-    <row r="47" ht="15">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>106</v>
       </c>
     </row>
-    <row r="48" ht="15">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>111</v>
       </c>
     </row>
-    <row r="49" ht="15">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>114</v>
       </c>
     </row>
-    <row r="50" ht="15">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="15">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>123</v>
       </c>
     </row>
-    <row r="52" ht="15">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>128</v>
       </c>
     </row>
-    <row r="53" ht="15">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>131</v>
       </c>
     </row>
-    <row r="54" ht="15">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>132</v>
       </c>
     </row>
-    <row r="55" ht="15">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>134</v>
       </c>
     </row>
-    <row r="56" ht="15">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>137</v>
       </c>
     </row>
-    <row r="57" ht="15">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>139</v>
       </c>
     </row>
-    <row r="58" ht="15">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>143</v>
       </c>
     </row>
-    <row r="59" ht="15">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>146</v>
       </c>
     </row>
-    <row r="60" ht="15">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>150</v>
       </c>
     </row>
-    <row r="61" ht="15">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>153</v>
       </c>
     </row>
-    <row r="62" ht="15">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>156</v>
       </c>
     </row>
-    <row r="63" ht="15">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>163</v>
       </c>
     </row>
-    <row r="64" ht="15">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>165</v>
       </c>
     </row>
-    <row r="65" ht="15">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>167</v>
       </c>
     </row>
-    <row r="66" ht="15">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>170</v>
       </c>
     </row>
-    <row r="67" ht="15">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>176</v>
       </c>
     </row>
-    <row r="68" ht="15">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>181</v>
       </c>
     </row>
-    <row r="69" ht="15">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>183</v>
       </c>
     </row>
-    <row r="70" ht="15">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>195</v>
       </c>
     </row>
-    <row r="71" ht="15">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>198</v>
       </c>
     </row>
-    <row r="72" ht="15">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>203</v>
       </c>
     </row>
-    <row r="73" ht="15">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>208</v>
       </c>
     </row>
-    <row r="74" ht="15">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>213</v>
       </c>
     </row>
-    <row r="75" ht="15">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>208</v>
       </c>
     </row>
-    <row r="76" ht="15">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>212</v>
       </c>
     </row>
-    <row r="77" ht="15">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>213</v>
       </c>
     </row>
-    <row r="78" ht="15">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>215</v>
       </c>
     </row>
-    <row r="79" ht="15">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>224</v>
       </c>
     </row>
-    <row r="80" ht="15">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>233</v>
       </c>
     </row>
-    <row r="81" ht="15">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>239</v>
       </c>
     </row>
-    <row r="82" ht="15">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>240</v>
       </c>
     </row>
-    <row r="83" ht="15">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>246</v>
       </c>
     </row>
-    <row r="84" ht="15">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>250</v>
       </c>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.54297" customWidth="1"/>
-    <col min="2" max="2" width="27.54297" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -927,7 +950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -935,7 +958,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -947,5 +970,6 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>https://www.clinicaveterinariapetitsipeluts.com/</t>
+  </si>
+  <si>
+    <t>Informática de la asociación A.A.</t>
+  </si>
+  <si>
+    <t>lauraisidro.com</t>
   </si>
 </sst>
 </file>
@@ -935,7 +941,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -966,6 +972,14 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>

--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\PaginaWeb\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\asociacionalmasbellas.github.io\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Colaboradores" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -59,36 +58,12 @@
 - Alfombrilla de lamer
 Gracias por el donativo a Articupets</t>
   </si>
-  <si>
-    <t>Colaborador</t>
-  </si>
-  <si>
-    <t>Enlace</t>
-  </si>
-  <si>
-    <t>ArticuPets</t>
-  </si>
-  <si>
-    <t>https://articupets.art/</t>
-  </si>
-  <si>
-    <t>Clínica Veterinària Petits i Peluts</t>
-  </si>
-  <si>
-    <t>https://www.clinicaveterinariapetitsipeluts.com/</t>
-  </si>
-  <si>
-    <t>Informática de la asociación A.A.</t>
-  </si>
-  <si>
-    <t>lauraisidro.com</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -100,21 +75,10 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF2B579A"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -132,57 +96,37 @@
     </fill>
   </fills>
   <borders count="2">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color rgb="FF2B579A"/>
       </right>
-      <top/>
       <bottom style="medium">
         <color rgb="FF2B579A"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="ConditionalFormatStyle" xfId="2"/>
-    <cellStyle name="HeaderStyle" xfId="3"/>
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ConditionalFormatStyle" xfId="1"/>
+    <cellStyle name="HeaderStyle" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -191,10 +135,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -326,6 +270,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -349,10 +294,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -361,13 +307,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -443,6 +389,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -462,26 +409,24 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F84"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="103.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.42578" customWidth="1"/>
+    <col min="2" max="2" width="23.85547" customWidth="1"/>
+    <col min="3" max="3" width="103.1406" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +437,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -506,7 +451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -514,7 +459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+    <row r="4" ht="165">
       <c r="A4">
         <v>3</v>
       </c>
@@ -525,7 +470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+    <row r="5" ht="180">
       <c r="A5">
         <v>4</v>
       </c>
@@ -537,453 +482,403 @@
       </c>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28">
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29">
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32">
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33">
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36">
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39">
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40">
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41">
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42">
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43">
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46">
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48">
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49">
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50">
         <v>119</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51">
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52">
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53">
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55">
         <v>134</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56">
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57">
         <v>139</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58">
         <v>143</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59">
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60">
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61">
         <v>153</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62">
         <v>156</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63">
         <v>163</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64">
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65">
         <v>167</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66">
         <v>170</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67">
         <v>176</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68">
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69">
         <v>183</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70">
         <v>195</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71">
         <v>198</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72">
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73">
         <v>208</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74">
         <v>213</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75">
         <v>208</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76">
         <v>212</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77">
         <v>213</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78">
         <v>215</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79">
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80">
         <v>233</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81">
         <v>239</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82">
         <v>240</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83">
         <v>246</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84">
         <v>250</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" paperSize="9" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -48,15 +48,7 @@
     <t>Descripcion Premio</t>
   </si>
   <si>
-    <t>En esta nueva rifa hemos querido sobre todo enfocarnos en los juegos y entretenimientos de los peludos, siendo los siguientes objetos los rifados:
-- Tres llaveros cuquísimos en versión animales (esto para el dueño)
-- Mordedor de cuerda con pelota y ventosa
-- Peluche de León multicolor
-- Pelota de goma con texturas
-- Alfombra olfativa pequeña
-- Dos pelotas Kong con sonido
-- Alfombrilla de lamer
-Gracias por el donativo a Articupets</t>
+    <t>En breves subiremos todos los premios de la rifa</t>
   </si>
 </sst>
 </file>
@@ -470,7 +462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="180">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>

--- a/assets/database/Rifa.xlsx
+++ b/assets/database/Rifa.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\asociacionalmasbellas.github.io\assets\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\PaginaWeb\assets\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Numeros comprados</t>
   </si>
@@ -37,25 +37,32 @@
   </si>
   <si>
     <t>Descripcion Rifa</t>
+  </si>
+  <si>
+    <t>Descripcion Premio</t>
+  </si>
+  <si>
+    <t>Cuando se vendan todos los númeritos del 1 al 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para DONATIVOS también se hace Bizum a Joan  indicando DONATIVO VIDA </t>
+  </si>
+  <si>
+    <t>2 euros</t>
   </si>
   <si>
     <t>Con VIDA llevamos algo más de un año apostando por su vida, por su oportunidad de normalizar, por su oportunidad de caminar más que menos .....
 Por ello apostamos por una guardería próxima, La Huella Azul, donde está la única veterinaria fisioterapeuta que aceptó venir a domicilio y que durante aproximadamente 9 meses está realizando la rehabilitación del pequeño.
 Volvemos con una Rifa para intentar sostener la rehabilitación, Bonos de 10 sesiones a 875€ que duran sobre un mes.
-Gracias a vuestra participación y a vuestros generosos donativos hemos podido renovar los Bonos durante este tiempo</t>
-  </si>
-  <si>
-    <t>Descripcion Premio</t>
-  </si>
-  <si>
-    <t>En breves subiremos todos los premios de la rifa</t>
+Gracias a vuestra participación y a vuestros generosos donativos hemos podido renovar los Bonos durante este tiempo
+Cómo se hace? Se envia un  whatsapp a Judith 608678808 y le dices los númeos que eliges y luego haces un Bizum a Joan  692160589  por el valor de la cantidad de numeros que hayas comprado (ej. 5 números  x 2 euros = 10 euros) indicando RIFA VIDA.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -71,6 +78,11 @@
       <sz val="11"/>
       <color rgb="FF2B579A"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -88,19 +100,28 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF2B579A"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF2B579A"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -113,12 +134,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="ConditionalFormatStyle" xfId="1"/>
     <cellStyle name="HeaderStyle" xfId="2"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -127,10 +156,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -262,7 +291,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -286,11 +314,10 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -299,13 +326,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -381,7 +408,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -401,24 +427,26 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F84"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.42578" customWidth="1"/>
-    <col min="2" max="2" width="23.85547" customWidth="1"/>
-    <col min="3" max="3" width="103.1406" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="103.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,29 +457,32 @@
         <v>250</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>2</v>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" ht="165">
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="210" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -459,418 +490,419 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>16</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>17</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>18</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>22</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>27</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>28</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>29</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>38</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>43</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>45</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>53</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>58</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>59</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>60</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>63</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>66</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>67</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>71</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>74</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>76</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>78</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>88</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>89</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>91</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>92</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>95</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>96</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>98</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>100</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>103</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>106</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>111</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>114</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>119</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>123</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>128</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>131</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>132</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>134</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>137</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>139</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>143</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>146</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>150</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>153</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>156</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>163</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>165</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>167</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>170</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>176</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>181</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>183</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>195</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>198</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>203</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>208</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>213</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>208</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>212</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>213</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>215</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>224</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>233</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>239</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>240</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>246</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>250</v>
       </c>
     </row>
   </sheetData>
-  <pageSetup r:id="rId1" paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>